--- a/surveyor_forms/020_municipal_waste_survey--surveyor_forms.xlsx
+++ b/surveyor_forms/020_municipal_waste_survey--surveyor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'recycling'}</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Recycling'}</t>
+          <t>Recycling</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'composting'}</t>
+          <t>composting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Composting'}</t>
+          <t>Composting</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'landfill'}</t>
+          <t>landfill</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Landfill'}</t>
+          <t>Landfill</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'organic'}</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Organic'}</t>
+          <t>Organic</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inorganic'}</t>
+          <t>inorganic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inorganic'}</t>
+          <t>Inorganic</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'glass'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Glass'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'curbside'}</t>
+          <t>curbside</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Curbside'}</t>
+          <t>Curbside</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'landfill'}</t>
+          <t>landfill</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Landfill'}</t>
+          <t>Landfill</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
